--- a/售前配置模板.xlsx
+++ b/售前配置模板.xlsx
@@ -13648,6 +13648,9 @@
       <c r="AG9">
         <v>10</v>
       </c>
+      <c r="AH9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" ht="27" spans="1:34">
       <c r="A10" s="6" t="s">
@@ -13730,9 +13733,6 @@
       </c>
       <c r="AG10" t="s">
         <v>4</v>
-      </c>
-      <c r="AH10">
-        <v>1</v>
       </c>
     </row>
     <row r="11" ht="94.5" spans="1:34">
